--- a/Doc/SimplePhotoFrame.xlsx
+++ b/Doc/SimplePhotoFrame.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\CQ_GOWIN_FPGA_Vol6\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75B3F16-DEAC-444B-957D-6C0BD2D58D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AF34FB-86FE-4E1F-9FE0-FFFD2A18B57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TangNano20K(LCD Controller)" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="135">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -281,13 +281,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>0'固定</t>
-    <rPh sb="2" eb="4">
-      <t>コテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>nc</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -581,6 +574,14 @@
   </si>
   <si>
     <t>fpga_spi_sck</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I2S_DOUT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I2S_EN</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -901,7 +902,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1025,26 +1026,32 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1530,14 +1537,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="15" x14ac:dyDescent="0.15">
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:16" x14ac:dyDescent="0.15">
@@ -1589,15 +1596,15 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="46" t="s">
         <v>51</v>
       </c>
       <c r="J4" s="5">
@@ -1630,15 +1637,15 @@
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="46"/>
       <c r="J5" s="5">
         <v>39</v>
       </c>
@@ -1669,15 +1676,15 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="44"/>
+      <c r="H6" s="46"/>
       <c r="J6" s="8">
         <v>38</v>
       </c>
@@ -1704,15 +1711,15 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="44"/>
+      <c r="H7" s="46"/>
       <c r="J7" s="8">
         <v>37</v>
       </c>
@@ -1726,13 +1733,13 @@
         <v>5</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>7</v>
       </c>
       <c r="P7" s="36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.15">
@@ -1746,7 +1753,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F8" s="27"/>
       <c r="G8" s="9"/>
@@ -1761,7 +1768,7 @@
         <v>4</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N8" s="27"/>
       <c r="O8" s="9"/>
@@ -1781,7 +1788,7 @@
         <v>23</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>7</v>
@@ -1797,7 +1804,7 @@
         <v>4</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N9" s="27"/>
       <c r="O9" s="9"/>
@@ -1817,7 +1824,7 @@
         <v>23</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>7</v>
@@ -1839,9 +1846,9 @@
         <v>57</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="P10" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="P10" s="45" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1856,7 +1863,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F11" s="27"/>
       <c r="G11" s="9"/>
@@ -1874,12 +1881,12 @@
         <v>56</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="P11" s="43"/>
+        <v>7</v>
+      </c>
+      <c r="P11" s="45"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="8">
@@ -1892,7 +1899,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F12" s="27"/>
       <c r="G12" s="9"/>
@@ -1909,13 +1916,13 @@
       <c r="M12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="N12" s="25" t="s">
+      <c r="N12" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="O12" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="O12" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="P12" s="17"/>
+      <c r="P12" s="49"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -1928,7 +1935,7 @@
         <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="27"/>
       <c r="G13" s="9"/>
@@ -1943,7 +1950,7 @@
         <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N13" s="27"/>
       <c r="O13" s="9"/>
@@ -1960,7 +1967,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F14" s="27"/>
       <c r="G14" s="9"/>
@@ -1981,7 +1988,7 @@
         <v>54</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P14" s="16" t="s">
         <v>58</v>
@@ -1998,7 +2005,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F15" s="27"/>
       <c r="G15" s="9"/>
@@ -2013,7 +2020,7 @@
         <v>3</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N15" s="27"/>
       <c r="O15" s="9"/>
@@ -2030,7 +2037,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F16" s="27"/>
       <c r="G16" s="9"/>
@@ -2060,7 +2067,7 @@
         <v>5</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F17" s="27"/>
       <c r="G17" s="9"/>
@@ -2078,7 +2085,7 @@
         <v>41</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>7</v>
@@ -2098,7 +2105,7 @@
         <v>23</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>7</v>
@@ -2137,7 +2144,7 @@
         <v>23</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>7</v>
@@ -2176,7 +2183,7 @@
         <v>23</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>7</v>
@@ -2192,8 +2199,8 @@
         <v>1</v>
       </c>
       <c r="M20" s="1"/>
-      <c r="N20" s="45" t="s">
-        <v>126</v>
+      <c r="N20" s="41" t="s">
+        <v>125</v>
       </c>
       <c r="O20" s="9" t="s">
         <v>7</v>
@@ -2214,7 +2221,7 @@
         <v>23</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>7</v>
@@ -2230,8 +2237,8 @@
         <v>1</v>
       </c>
       <c r="M21" s="1"/>
-      <c r="N21" s="45" t="s">
-        <v>125</v>
+      <c r="N21" s="41" t="s">
+        <v>124</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>7</v>
@@ -2348,13 +2355,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B1" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
+      <c r="B1" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
       <c r="G1" s="18"/>
     </row>
     <row r="2" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -2395,7 +2402,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -2405,7 +2412,7 @@
         <v>40</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -2418,7 +2425,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -2428,7 +2435,7 @@
         <v>39</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -2462,7 +2469,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -2472,7 +2479,7 @@
         <v>37</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -2484,11 +2491,11 @@
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>6</v>
@@ -2498,7 +2505,7 @@
         <v>36</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -2512,13 +2519,13 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>6</v>
@@ -2528,7 +2535,7 @@
         <v>35</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -2540,13 +2547,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>7</v>
@@ -2556,7 +2563,7 @@
         <v>34</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -2590,13 +2597,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>7</v>
@@ -2606,7 +2613,7 @@
         <v>32</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="25"/>
@@ -2618,13 +2625,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>7</v>
@@ -2634,7 +2641,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -2646,13 +2653,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>6</v>
@@ -2662,7 +2669,7 @@
         <v>30</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -2674,13 +2681,13 @@
         <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>7</v>
@@ -2690,7 +2697,7 @@
         <v>29</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="29"/>
@@ -2724,13 +2731,13 @@
         <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>7</v>
@@ -2740,11 +2747,11 @@
         <v>27</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K17" s="1"/>
-      <c r="L17" s="46" t="s">
-        <v>130</v>
+      <c r="L17" s="42" t="s">
+        <v>129</v>
       </c>
       <c r="M17" s="9" t="s">
         <v>6</v>
@@ -2755,13 +2762,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>7</v>
@@ -2771,11 +2778,11 @@
         <v>26</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K18" s="1"/>
-      <c r="L18" s="46" t="s">
-        <v>129</v>
+      <c r="L18" s="42" t="s">
+        <v>128</v>
       </c>
       <c r="M18" s="9" t="s">
         <v>6</v>
@@ -2786,7 +2793,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -2796,11 +2803,11 @@
         <v>25</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K19" s="1"/>
-      <c r="L19" s="46" t="s">
-        <v>128</v>
+      <c r="L19" s="42" t="s">
+        <v>127</v>
       </c>
       <c r="M19" s="9" t="s">
         <v>6</v>
@@ -2811,7 +2818,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -2821,11 +2828,11 @@
         <v>24</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K20" s="1"/>
-      <c r="L20" s="46" t="s">
-        <v>127</v>
+      <c r="L20" s="42" t="s">
+        <v>126</v>
       </c>
       <c r="M20" s="9" t="s">
         <v>6</v>
@@ -2859,7 +2866,7 @@
         <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -2868,11 +2875,11 @@
         <v>22</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K22" s="1"/>
-      <c r="L22" s="46" t="s">
-        <v>132</v>
+      <c r="L22" s="42" t="s">
+        <v>131</v>
       </c>
       <c r="M22" s="9" t="s">
         <v>6</v>
@@ -2883,7 +2890,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="21"/>
@@ -2892,11 +2899,11 @@
         <v>21</v>
       </c>
       <c r="J23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K23" s="21"/>
-      <c r="L23" s="47" t="s">
-        <v>131</v>
+      <c r="L23" s="43" t="s">
+        <v>130</v>
       </c>
       <c r="M23" s="22" t="s">
         <v>6</v>
@@ -2910,7 +2917,7 @@
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.15">
       <c r="M30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.15">
@@ -2924,7 +2931,7 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.15">
       <c r="L32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M32" s="38"/>
       <c r="N32" s="1" t="s">
@@ -2933,25 +2940,25 @@
     </row>
     <row r="33" spans="12:14" x14ac:dyDescent="0.15">
       <c r="L33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M33" s="39"/>
       <c r="N33" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="12:14" x14ac:dyDescent="0.15">
       <c r="L34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M34" s="40"/>
       <c r="N34" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="12:14" x14ac:dyDescent="0.15">
       <c r="L38" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Doc/SimplePhotoFrame.xlsx
+++ b/Doc/SimplePhotoFrame.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\CQ_GOWIN_FPGA_Vol6\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AF34FB-86FE-4E1F-9FE0-FFFD2A18B57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E67554-2A9D-418F-831E-70B3DFEBF194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TangNano20K(LCD Controller)" sheetId="4" r:id="rId1"/>
     <sheet name="RasPiPico2W" sheetId="8" r:id="rId2"/>
+    <sheet name="DisplaySignal" sheetId="9" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="161">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -582,6 +583,134 @@
   </si>
   <si>
     <t>I2S_EN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フロントポーチ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同期幅</t>
+    <rPh sb="0" eb="3">
+      <t>ドウキハバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バックポーチ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>映像期間</t>
+    <rPh sb="0" eb="2">
+      <t>エイゾウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水平</t>
+    <rPh sb="0" eb="2">
+      <t>スイヘイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>垂直</t>
+    <rPh sb="0" eb="2">
+      <t>スイチョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>映像期間</t>
+    <rPh sb="0" eb="4">
+      <t>エイゾウキカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>動作クロック</t>
+    <rPh sb="0" eb="2">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MHz</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>line</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pixel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リフレッシュレート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hz</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TOTAL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フレーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>clock</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秒間</t>
+    <rPh sb="0" eb="2">
+      <t>ビョウカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>H Pulse Width</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>V Pulse Width</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>H Back Porch</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>H Front Porch</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>V Back Porch</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>V Front Porch</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>V Active Area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>H Active Area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>frame</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -629,7 +758,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -708,6 +837,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -902,7 +1037,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1035,6 +1170,12 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1047,11 +1188,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1537,14 +1678,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="15" x14ac:dyDescent="0.15">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:16" x14ac:dyDescent="0.15">
@@ -1604,7 +1745,7 @@
       <c r="G4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="46" t="s">
+      <c r="H4" s="48" t="s">
         <v>51</v>
       </c>
       <c r="J4" s="5">
@@ -1645,7 +1786,7 @@
       <c r="G5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="46"/>
+      <c r="H5" s="48"/>
       <c r="J5" s="5">
         <v>39</v>
       </c>
@@ -1684,7 +1825,7 @@
       <c r="G6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="46"/>
+      <c r="H6" s="48"/>
       <c r="J6" s="8">
         <v>38</v>
       </c>
@@ -1719,7 +1860,7 @@
       <c r="G7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="46"/>
+      <c r="H7" s="48"/>
       <c r="J7" s="8">
         <v>37</v>
       </c>
@@ -1848,7 +1989,7 @@
       <c r="O10" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P10" s="45" t="s">
+      <c r="P10" s="47" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1886,7 +2027,7 @@
       <c r="O11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P11" s="45"/>
+      <c r="P11" s="47"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="8">
@@ -1916,13 +2057,13 @@
       <c r="M12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="N12" s="48" t="s">
+      <c r="N12" s="44" t="s">
         <v>134</v>
       </c>
       <c r="O12" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="P12" s="49"/>
+      <c r="P12" s="45"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -2355,13 +2496,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
       <c r="G1" s="18"/>
     </row>
     <row r="2" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -2969,4 +3110,222 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4BE3BB3-64AB-47EA-BE6E-B1280D7BB1A8}">
+  <dimension ref="A2:E20"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B3" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="1">
+        <v>20</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B4" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="51">
+        <v>46</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="50">
+        <v>800</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B6" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="51">
+        <v>210</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B7" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1">
+        <f>SUM(D4:D6)</f>
+        <v>1056</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" s="1">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="51">
+        <v>23</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B12" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D12" s="50">
+        <v>480</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B13" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D13" s="51">
+        <v>18</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B14" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1">
+        <f>SUM(D11:D13)</f>
+        <v>521</v>
+      </c>
+      <c r="E14" s="50" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1">
+        <f>D7*D14</f>
+        <v>550176</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1">
+        <f>(D19*1000000)/D16</f>
+        <v>59.980806142034552</v>
+      </c>
+      <c r="E17" s="50" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1">
+        <v>33</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1">
+        <v>60</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>